--- a/XBRL-template-MFRS/10-Notes-CorporateInfo.xlsx
+++ b/XBRL-template-MFRS/10-Notes-CorporateInfo.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +43,15 @@
     <font>
       <name val="Arial"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
@@ -89,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -107,6 +116,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -482,12 +497,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>

--- a/XBRL-template-MFRS/10-Notes-CorporateInfo.xlsx
+++ b/XBRL-template-MFRS/10-Notes-CorporateInfo.xlsx
@@ -16,8 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
+  </numFmts>
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,8 +55,48 @@
       <name val="Arial"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -71,8 +113,20 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+        <bgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -94,11 +148,22 @@
         <color rgb="00B0B0B0"/>
       </bottom>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="001F3864"/>
+      </bottom>
+    </border>
+    <border/>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9DEE5"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -122,6 +187,36 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -488,86 +583,99 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="9" t="inlineStr">
+    <row r="1" ht="20" customHeight="1">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>01/01/YYYY - 31/12/YYYY</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="D1" s="17" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>Notes - Corporate information</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="D3" s="11" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Corporate information</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="B4" s="13" t="n"/>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="18" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>*Disclosure of corporate information</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="19" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Financial reporting status</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="18" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Explanation of reasons for the restatement of previous financial statements figures</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="19" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Explanation of reasons for the reclassification of previous financial statements figures</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="19" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Explanation of reasons for using longer or shorter reporting period</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="19" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
